--- a/_doi-chieu-gia.xlsx
+++ b/_doi-chieu-gia.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="44">
   <si>
     <t>Mã</t>
   </si>
@@ -101,117 +101,6 @@
   </si>
   <si>
     <t>MUCO ROSE</t>
-  </si>
-  <si>
-    <t>G-007</t>
-  </si>
-  <si>
-    <t>NHÀ CỦA HOON</t>
-  </si>
-  <si>
-    <t>(băng-rôn chỉ nói về NCB 01 (Căn trước), NCB 02 (Căn sau)) NCB 01,02 kê ko quá 500k/ đêm</t>
-  </si>
-  <si>
-    <t>G-008</t>
-  </si>
-  <si>
-    <t>XÓM LÈO HOMESTAY</t>
-  </si>
-  <si>
-    <t>G-027</t>
-  </si>
-  <si>
-    <t>MYA VILLA</t>
-  </si>
-  <si>
-    <t>G-028</t>
-  </si>
-  <si>
-    <t>SUNSHINE VILLA</t>
-  </si>
-  <si>
-    <t>G-029</t>
-  </si>
-  <si>
-    <t>KQH AN SƠN VILLA</t>
-  </si>
-  <si>
-    <t>G-032</t>
-  </si>
-  <si>
-    <t>NCB 01 VILLA</t>
-  </si>
-  <si>
-    <t>G-033</t>
-  </si>
-  <si>
-    <t>NCB 02 VILLA</t>
-  </si>
-  <si>
-    <t>G-034</t>
-  </si>
-  <si>
-    <t>ẤM HOMESTAY</t>
-  </si>
-  <si>
-    <t>G-035</t>
-  </si>
-  <si>
-    <t>NHÀ CỦA GẤU</t>
-  </si>
-  <si>
-    <t>G-092</t>
-  </si>
-  <si>
-    <t>La Beau Rêve</t>
-  </si>
-  <si>
-    <t>G-093</t>
-  </si>
-  <si>
-    <t>NC05</t>
-  </si>
-  <si>
-    <t>G-036</t>
-  </si>
-  <si>
-    <t>FAIRY HOMESTAY</t>
-  </si>
-  <si>
-    <t>G-037</t>
-  </si>
-  <si>
-    <t>MƠ HOMESTAY</t>
-  </si>
-  <si>
-    <t>G-038</t>
-  </si>
-  <si>
-    <t>NCB 03 VILLA</t>
-  </si>
-  <si>
-    <t>G-039</t>
-  </si>
-  <si>
-    <t>NCB 04 VILLA</t>
-  </si>
-  <si>
-    <t>G-041</t>
-  </si>
-  <si>
-    <t>GẠCH HOMESTAY</t>
-  </si>
-  <si>
-    <t>G-070</t>
-  </si>
-  <si>
-    <t>LA FOREST ĐƠN 201</t>
-  </si>
-  <si>
-    <t>G-081</t>
-  </si>
-  <si>
-    <t>NHÀ CỦA GẤU 3</t>
   </si>
   <si>
     <t>G-062</t>
@@ -653,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -970,62 +859,62 @@
         <v>31</v>
       </c>
       <c r="C8" s="4">
-        <v>3000000</v>
-      </c>
-      <c r="D8" s="4">
-        <v>3000000</v>
-      </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4">
-        <v>4000000</v>
-      </c>
+        <v>1700000</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="F8" s="4"/>
       <c r="G8" s="4">
-        <v>400000</v>
+        <v>300000</v>
       </c>
       <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
+      <c r="I8" s="4">
+        <v>600000</v>
+      </c>
       <c r="J8" s="4"/>
       <c r="K8" s="4">
-        <v>3400000</v>
+        <v>2000000</v>
       </c>
       <c r="L8" s="4">
-        <v>3400000</v>
+        <v>2000000</v>
       </c>
       <c r="M8" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="N8" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
         <v>33</v>
       </c>
-      <c r="B9" t="s">
-        <v>34</v>
-      </c>
       <c r="C9" s="4">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4">
-        <v>2500000</v>
+        <v>1800000</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4">
-        <v>400000</v>
+        <v>300000</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="4">
-        <v>800000</v>
+        <v>600000</v>
       </c>
       <c r="J9" s="4"/>
       <c r="K9" s="4">
-        <v>2400000</v>
+        <v>1800000</v>
       </c>
       <c r="L9" s="4">
-        <v>2400000</v>
+        <v>1800000</v>
       </c>
       <c r="M9" t="s">
         <v>17</v>
@@ -1036,79 +925,75 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
         <v>35</v>
       </c>
-      <c r="B10" t="s">
-        <v>36</v>
-      </c>
       <c r="C10" s="4">
-        <v>3500000</v>
-      </c>
-      <c r="D10" s="4">
-        <v>3500000</v>
-      </c>
-      <c r="E10" s="2">
-        <v>4500000</v>
-      </c>
-      <c r="F10" s="3">
-        <v>4000000</v>
-      </c>
+        <v>1500000</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4">
+        <v>1800000</v>
+      </c>
+      <c r="F10" s="4"/>
       <c r="G10" s="4">
-        <v>500000</v>
+        <v>300000</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="4">
-        <v>1000000</v>
+        <v>600000</v>
       </c>
       <c r="J10" s="4"/>
       <c r="K10" s="4">
-        <v>4000000</v>
+        <v>1800000</v>
       </c>
       <c r="L10" s="4">
-        <v>4000000</v>
+        <v>1800000</v>
       </c>
       <c r="M10" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="N10" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" t="s">
         <v>37</v>
       </c>
-      <c r="B11" t="s">
-        <v>38</v>
-      </c>
       <c r="C11" s="2">
-        <v>2500000</v>
+        <v>800000</v>
       </c>
       <c r="D11" s="3">
-        <v>2000000</v>
+        <v>750000</v>
       </c>
       <c r="E11" s="2">
-        <v>3000000</v>
+        <v>800000</v>
       </c>
       <c r="F11" s="3">
-        <v>2800000</v>
+        <v>750000</v>
       </c>
       <c r="G11" s="4">
-        <v>400000</v>
+        <v>150000</v>
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="4">
-        <v>800000</v>
+        <v>300000</v>
       </c>
       <c r="J11" s="4"/>
       <c r="K11" s="4">
-        <v>2900000</v>
+        <v>950000</v>
       </c>
       <c r="L11" s="4">
-        <v>2400000</v>
+        <v>900000</v>
       </c>
       <c r="M11" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="N11" t="s">
         <v>17</v>
@@ -1116,39 +1001,39 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
         <v>39</v>
       </c>
-      <c r="B12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" s="4">
-        <v>2500000</v>
-      </c>
-      <c r="D12" s="4">
-        <v>2500000</v>
+      <c r="C12" s="2">
+        <v>800000</v>
+      </c>
+      <c r="D12" s="3">
+        <v>750000</v>
       </c>
       <c r="E12" s="2">
-        <v>3500000</v>
+        <v>800000</v>
       </c>
       <c r="F12" s="3">
-        <v>3000000</v>
+        <v>750000</v>
       </c>
       <c r="G12" s="4">
-        <v>400000</v>
+        <v>150000</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="4">
-        <v>800000</v>
+        <v>300000</v>
       </c>
       <c r="J12" s="4"/>
       <c r="K12" s="4">
-        <v>2900000</v>
+        <v>950000</v>
       </c>
       <c r="L12" s="4">
-        <v>2900000</v>
+        <v>900000</v>
       </c>
       <c r="M12" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="N12" t="s">
         <v>17</v>
@@ -1156,32 +1041,32 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" t="s">
         <v>41</v>
       </c>
-      <c r="B13" t="s">
-        <v>42</v>
-      </c>
       <c r="C13" s="4">
-        <v>1600000</v>
+        <v>600000</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4">
-        <v>1800000</v>
+        <v>600000</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="4">
-        <v>300000</v>
+        <v>150000</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="4">
-        <v>600000</v>
+        <v>300000</v>
       </c>
       <c r="J13" s="4"/>
       <c r="K13" s="4">
-        <v>1900000</v>
+        <v>750000</v>
       </c>
       <c r="L13" s="4">
-        <v>1900000</v>
+        <v>750000</v>
       </c>
       <c r="M13" t="s">
         <v>17</v>
@@ -1192,731 +1077,37 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" t="s">
         <v>43</v>
       </c>
-      <c r="B14" t="s">
-        <v>44</v>
-      </c>
       <c r="C14" s="4">
-        <v>2000000</v>
+        <v>4000000</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4">
-        <v>2400000</v>
+        <v>4500000</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4">
-        <v>400000</v>
+        <v>500000</v>
       </c>
       <c r="H14" s="4"/>
       <c r="I14" s="4">
-        <v>800000</v>
+        <v>1000000</v>
       </c>
       <c r="J14" s="4"/>
       <c r="K14" s="4">
-        <v>2400000</v>
+        <v>4500000</v>
       </c>
       <c r="L14" s="4">
-        <v>2400000</v>
+        <v>4500000</v>
       </c>
       <c r="M14" t="s">
         <v>17</v>
       </c>
       <c r="N14" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="4">
-        <v>1600000</v>
-      </c>
-      <c r="D15" s="4">
-        <v>1600000</v>
-      </c>
-      <c r="E15" s="4">
-        <v>2200000</v>
-      </c>
-      <c r="F15" s="4">
-        <v>2200000</v>
-      </c>
-      <c r="G15" s="4">
-        <v>300000</v>
-      </c>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4">
-        <v>600000</v>
-      </c>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4">
-        <v>1900000</v>
-      </c>
-      <c r="L15" s="4">
-        <v>1900000</v>
-      </c>
-      <c r="M15" t="s">
-        <v>32</v>
-      </c>
-      <c r="N15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" s="4">
-        <v>1300000</v>
-      </c>
-      <c r="D16" s="4">
-        <v>1300000</v>
-      </c>
-      <c r="E16" s="4">
-        <v>1800000</v>
-      </c>
-      <c r="F16" s="4">
-        <v>1800000</v>
-      </c>
-      <c r="G16" s="4">
-        <v>300000</v>
-      </c>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4">
-        <v>600000</v>
-      </c>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4">
-        <v>1600000</v>
-      </c>
-      <c r="L16" s="4">
-        <v>1600000</v>
-      </c>
-      <c r="M16" t="s">
-        <v>32</v>
-      </c>
-      <c r="N16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>49</v>
-      </c>
-      <c r="B17" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" s="2">
-        <v>2300000</v>
-      </c>
-      <c r="D17" s="3">
-        <v>2000000</v>
-      </c>
-      <c r="E17" s="2">
-        <v>2800000</v>
-      </c>
-      <c r="F17" s="3">
-        <v>2500000</v>
-      </c>
-      <c r="G17" s="4">
-        <v>400000</v>
-      </c>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4">
-        <v>800000</v>
-      </c>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4">
-        <v>2700000</v>
-      </c>
-      <c r="L17" s="4">
-        <v>2400000</v>
-      </c>
-      <c r="M17" t="s">
-        <v>32</v>
-      </c>
-      <c r="N17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" t="s">
-        <v>52</v>
-      </c>
-      <c r="C18" s="4">
-        <v>3000000</v>
-      </c>
-      <c r="D18" s="4">
-        <v>3000000</v>
-      </c>
-      <c r="E18" s="4">
-        <v>3500000</v>
-      </c>
-      <c r="F18" s="4">
-        <v>3500000</v>
-      </c>
-      <c r="G18" s="4">
-        <v>400000</v>
-      </c>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4">
-        <v>800000</v>
-      </c>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4">
-        <v>3400000</v>
-      </c>
-      <c r="L18" s="4">
-        <v>3400000</v>
-      </c>
-      <c r="M18" t="s">
-        <v>32</v>
-      </c>
-      <c r="N18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>53</v>
-      </c>
-      <c r="B19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C19" s="4">
-        <v>1500000</v>
-      </c>
-      <c r="D19" s="4">
-        <v>1500000</v>
-      </c>
-      <c r="E19" s="4">
-        <v>1800000</v>
-      </c>
-      <c r="F19" s="4">
-        <v>1800000</v>
-      </c>
-      <c r="G19" s="4">
-        <v>300000</v>
-      </c>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4">
-        <v>600000</v>
-      </c>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4">
-        <v>1800000</v>
-      </c>
-      <c r="L19" s="4">
-        <v>1800000</v>
-      </c>
-      <c r="M19" t="s">
-        <v>32</v>
-      </c>
-      <c r="N19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B20" t="s">
-        <v>56</v>
-      </c>
-      <c r="C20" s="2">
-        <v>1500000</v>
-      </c>
-      <c r="D20" s="3">
-        <v>1200000</v>
-      </c>
-      <c r="E20" s="2">
-        <v>2000000</v>
-      </c>
-      <c r="F20" s="3">
-        <v>1200000</v>
-      </c>
-      <c r="G20" s="4">
-        <v>300000</v>
-      </c>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4">
-        <v>600000</v>
-      </c>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4">
-        <v>1800000</v>
-      </c>
-      <c r="L20" s="4">
-        <v>1500000</v>
-      </c>
-      <c r="M20" t="s">
-        <v>32</v>
-      </c>
-      <c r="N20" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>57</v>
-      </c>
-      <c r="B21" t="s">
-        <v>58</v>
-      </c>
-      <c r="C21" s="2">
-        <v>1100000</v>
-      </c>
-      <c r="D21" s="3">
-        <v>1200000</v>
-      </c>
-      <c r="E21" s="4">
-        <v>1300000</v>
-      </c>
-      <c r="F21" s="4">
-        <v>1300000</v>
-      </c>
-      <c r="G21" s="4">
-        <v>300000</v>
-      </c>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4">
-        <v>600000</v>
-      </c>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4">
-        <v>1400000</v>
-      </c>
-      <c r="L21" s="4">
-        <v>1500000</v>
-      </c>
-      <c r="M21" t="s">
-        <v>32</v>
-      </c>
-      <c r="N21" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>59</v>
-      </c>
-      <c r="B22" t="s">
-        <v>60</v>
-      </c>
-      <c r="C22" s="2">
-        <v>1100000</v>
-      </c>
-      <c r="D22" s="3">
-        <v>1000000</v>
-      </c>
-      <c r="E22" s="2">
-        <v>1300000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>1100000</v>
-      </c>
-      <c r="G22" s="4">
-        <v>300000</v>
-      </c>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4">
-        <v>600000</v>
-      </c>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4">
-        <v>1400000</v>
-      </c>
-      <c r="L22" s="4">
-        <v>1300000</v>
-      </c>
-      <c r="M22" t="s">
-        <v>32</v>
-      </c>
-      <c r="N22" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>61</v>
-      </c>
-      <c r="B23" t="s">
-        <v>62</v>
-      </c>
-      <c r="C23" s="2">
-        <v>400000</v>
-      </c>
-      <c r="D23" s="3">
-        <v>300000</v>
-      </c>
-      <c r="E23" s="2">
-        <v>500000</v>
-      </c>
-      <c r="F23" s="3">
-        <v>300000</v>
-      </c>
-      <c r="G23" s="4">
-        <v>150000</v>
-      </c>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4">
-        <v>300000</v>
-      </c>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4">
-        <v>550000</v>
-      </c>
-      <c r="L23" s="4">
-        <v>450000</v>
-      </c>
-      <c r="M23" t="s">
-        <v>32</v>
-      </c>
-      <c r="N23" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>63</v>
-      </c>
-      <c r="B24" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" s="4">
-        <v>600000</v>
-      </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4">
-        <v>600000</v>
-      </c>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4">
-        <v>150000</v>
-      </c>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4">
-        <v>300000</v>
-      </c>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4">
-        <v>750000</v>
-      </c>
-      <c r="L24" s="4">
-        <v>750000</v>
-      </c>
-      <c r="M24" t="s">
-        <v>17</v>
-      </c>
-      <c r="N24" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>65</v>
-      </c>
-      <c r="B25" t="s">
-        <v>66</v>
-      </c>
-      <c r="C25" s="4">
-        <v>800000</v>
-      </c>
-      <c r="D25" s="4">
-        <v>800000</v>
-      </c>
-      <c r="E25" s="2">
-        <v>900000</v>
-      </c>
-      <c r="F25" s="3">
-        <v>1000000</v>
-      </c>
-      <c r="G25" s="4">
-        <v>150000</v>
-      </c>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4">
-        <v>950000</v>
-      </c>
-      <c r="L25" s="4">
-        <v>950000</v>
-      </c>
-      <c r="M25" t="s">
-        <v>32</v>
-      </c>
-      <c r="N25" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>67</v>
-      </c>
-      <c r="B26" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26" s="4">
-        <v>1700000</v>
-      </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4">
-        <v>2000000</v>
-      </c>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4">
-        <v>300000</v>
-      </c>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4">
-        <v>600000</v>
-      </c>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4">
-        <v>2000000</v>
-      </c>
-      <c r="L26" s="4">
-        <v>2000000</v>
-      </c>
-      <c r="M26" t="s">
-        <v>17</v>
-      </c>
-      <c r="N26" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>69</v>
-      </c>
-      <c r="B27" t="s">
-        <v>70</v>
-      </c>
-      <c r="C27" s="4">
-        <v>1500000</v>
-      </c>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4">
-        <v>1800000</v>
-      </c>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4">
-        <v>300000</v>
-      </c>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4">
-        <v>600000</v>
-      </c>
-      <c r="J27" s="4"/>
-      <c r="K27" s="4">
-        <v>1800000</v>
-      </c>
-      <c r="L27" s="4">
-        <v>1800000</v>
-      </c>
-      <c r="M27" t="s">
-        <v>17</v>
-      </c>
-      <c r="N27" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>71</v>
-      </c>
-      <c r="B28" t="s">
-        <v>72</v>
-      </c>
-      <c r="C28" s="4">
-        <v>1500000</v>
-      </c>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4">
-        <v>1800000</v>
-      </c>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4">
-        <v>300000</v>
-      </c>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4">
-        <v>600000</v>
-      </c>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4">
-        <v>1800000</v>
-      </c>
-      <c r="L28" s="4">
-        <v>1800000</v>
-      </c>
-      <c r="M28" t="s">
-        <v>17</v>
-      </c>
-      <c r="N28" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>73</v>
-      </c>
-      <c r="B29" t="s">
-        <v>74</v>
-      </c>
-      <c r="C29" s="2">
-        <v>800000</v>
-      </c>
-      <c r="D29" s="3">
-        <v>750000</v>
-      </c>
-      <c r="E29" s="2">
-        <v>800000</v>
-      </c>
-      <c r="F29" s="3">
-        <v>750000</v>
-      </c>
-      <c r="G29" s="4">
-        <v>150000</v>
-      </c>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4">
-        <v>300000</v>
-      </c>
-      <c r="J29" s="4"/>
-      <c r="K29" s="4">
-        <v>950000</v>
-      </c>
-      <c r="L29" s="4">
-        <v>900000</v>
-      </c>
-      <c r="M29" t="s">
-        <v>17</v>
-      </c>
-      <c r="N29" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>75</v>
-      </c>
-      <c r="B30" t="s">
-        <v>76</v>
-      </c>
-      <c r="C30" s="2">
-        <v>800000</v>
-      </c>
-      <c r="D30" s="3">
-        <v>750000</v>
-      </c>
-      <c r="E30" s="2">
-        <v>800000</v>
-      </c>
-      <c r="F30" s="3">
-        <v>750000</v>
-      </c>
-      <c r="G30" s="4">
-        <v>150000</v>
-      </c>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4">
-        <v>300000</v>
-      </c>
-      <c r="J30" s="4"/>
-      <c r="K30" s="4">
-        <v>950000</v>
-      </c>
-      <c r="L30" s="4">
-        <v>900000</v>
-      </c>
-      <c r="M30" t="s">
-        <v>17</v>
-      </c>
-      <c r="N30" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>77</v>
-      </c>
-      <c r="B31" t="s">
-        <v>78</v>
-      </c>
-      <c r="C31" s="4">
-        <v>600000</v>
-      </c>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4">
-        <v>600000</v>
-      </c>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4">
-        <v>150000</v>
-      </c>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4">
-        <v>300000</v>
-      </c>
-      <c r="J31" s="4"/>
-      <c r="K31" s="4">
-        <v>750000</v>
-      </c>
-      <c r="L31" s="4">
-        <v>750000</v>
-      </c>
-      <c r="M31" t="s">
-        <v>17</v>
-      </c>
-      <c r="N31" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>79</v>
-      </c>
-      <c r="B32" t="s">
-        <v>80</v>
-      </c>
-      <c r="C32" s="4">
-        <v>4000000</v>
-      </c>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4">
-        <v>4500000</v>
-      </c>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4">
-        <v>500000</v>
-      </c>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4">
-        <v>1000000</v>
-      </c>
-      <c r="J32" s="4"/>
-      <c r="K32" s="4">
-        <v>4500000</v>
-      </c>
-      <c r="L32" s="4">
-        <v>4500000</v>
-      </c>
-      <c r="M32" t="s">
-        <v>17</v>
-      </c>
-      <c r="N32" t="s">
         <v>17</v>
       </c>
     </row>

--- a/_doi-chieu-gia.xlsx
+++ b/_doi-chieu-gia.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="191">
   <si>
     <t>Mã</t>
   </si>
@@ -103,6 +103,252 @@
     <t>MUCO ROSE</t>
   </si>
   <si>
+    <t>G-007</t>
+  </si>
+  <si>
+    <t>NHÀ CỦA HOON</t>
+  </si>
+  <si>
+    <t>(băng-rôn chỉ nói về NCB 01 (Căn trước), NCB 02 (Căn sau)) NCB 01,02 kê ko quá 500k/ đêm</t>
+  </si>
+  <si>
+    <t>G-008</t>
+  </si>
+  <si>
+    <t>XÓM LÈO HOMESTAY</t>
+  </si>
+  <si>
+    <t>G-027</t>
+  </si>
+  <si>
+    <t>MYA VILLA</t>
+  </si>
+  <si>
+    <t>G-028</t>
+  </si>
+  <si>
+    <t>SUNSHINE VILLA</t>
+  </si>
+  <si>
+    <t>G-029</t>
+  </si>
+  <si>
+    <t>KQH AN SƠN VILLA</t>
+  </si>
+  <si>
+    <t>G-032</t>
+  </si>
+  <si>
+    <t>NCB 01 VILLA</t>
+  </si>
+  <si>
+    <t>G-033</t>
+  </si>
+  <si>
+    <t>NCB 02 VILLA</t>
+  </si>
+  <si>
+    <t>G-034</t>
+  </si>
+  <si>
+    <t>ẤM HOMESTAY</t>
+  </si>
+  <si>
+    <t>G-035</t>
+  </si>
+  <si>
+    <t>NHÀ CỦA GẤU</t>
+  </si>
+  <si>
+    <t>G-092</t>
+  </si>
+  <si>
+    <t>La Beau Rêve</t>
+  </si>
+  <si>
+    <t>G-093</t>
+  </si>
+  <si>
+    <t>NC05</t>
+  </si>
+  <si>
+    <t>G-036</t>
+  </si>
+  <si>
+    <t>FAIRY HOMESTAY</t>
+  </si>
+  <si>
+    <t>G-037</t>
+  </si>
+  <si>
+    <t>MƠ HOMESTAY</t>
+  </si>
+  <si>
+    <t>G-038</t>
+  </si>
+  <si>
+    <t>NCB 03 VILLA</t>
+  </si>
+  <si>
+    <t>G-039</t>
+  </si>
+  <si>
+    <t>NCB 04 VILLA</t>
+  </si>
+  <si>
+    <t>G-041</t>
+  </si>
+  <si>
+    <t>GẠCH HOMESTAY</t>
+  </si>
+  <si>
+    <t>G-070</t>
+  </si>
+  <si>
+    <t>LA FOREST ĐƠN 201</t>
+  </si>
+  <si>
+    <t>G-081</t>
+  </si>
+  <si>
+    <t>NHÀ CỦA GẤU 3</t>
+  </si>
+  <si>
+    <t>G-009</t>
+  </si>
+  <si>
+    <t>MĂNG LIN VILLA</t>
+  </si>
+  <si>
+    <t>G-082</t>
+  </si>
+  <si>
+    <t>VILLA ADV</t>
+  </si>
+  <si>
+    <t>G-084</t>
+  </si>
+  <si>
+    <t>VILLA BẠCH ĐẰNG</t>
+  </si>
+  <si>
+    <t>G-021</t>
+  </si>
+  <si>
+    <t>KÉN HOMESTAY</t>
+  </si>
+  <si>
+    <t>G-022</t>
+  </si>
+  <si>
+    <t>KÉN HOUSE 2</t>
+  </si>
+  <si>
+    <t>GIÁ THU VỀ, chênh 300-500k/đêm ngày thường, không quá 1tr/đêm Tết</t>
+  </si>
+  <si>
+    <t>G-023</t>
+  </si>
+  <si>
+    <t>ĐÔNG PHƯƠNG VILLA</t>
+  </si>
+  <si>
+    <t>G-026</t>
+  </si>
+  <si>
+    <t>HD1</t>
+  </si>
+  <si>
+    <t>G-031</t>
+  </si>
+  <si>
+    <t>CAO THẮNG</t>
+  </si>
+  <si>
+    <t>CHÊNH MAX 200K</t>
+  </si>
+  <si>
+    <t>G-061</t>
+  </si>
+  <si>
+    <t>CAMI 1</t>
+  </si>
+  <si>
+    <t>G-080</t>
+  </si>
+  <si>
+    <t>SABIHOME</t>
+  </si>
+  <si>
+    <t>G-063</t>
+  </si>
+  <si>
+    <t>NẤM HOME</t>
+  </si>
+  <si>
+    <t>G-066</t>
+  </si>
+  <si>
+    <t>NGÕ THÔNG</t>
+  </si>
+  <si>
+    <t>G-040</t>
+  </si>
+  <si>
+    <t>A15</t>
+  </si>
+  <si>
+    <t>G-050</t>
+  </si>
+  <si>
+    <t>KING 1 VILLA</t>
+  </si>
+  <si>
+    <t>Ngày thường chênh tối đa 700k, lễ/ Tết tối đa 1tr</t>
+  </si>
+  <si>
+    <t>G-051</t>
+  </si>
+  <si>
+    <t>KING 3 VILLA</t>
+  </si>
+  <si>
+    <t>G-052</t>
+  </si>
+  <si>
+    <t>CHAN CHAN VILLA</t>
+  </si>
+  <si>
+    <t>G-053</t>
+  </si>
+  <si>
+    <t>VILLA TRỊNH HOÀI ĐỨC</t>
+  </si>
+  <si>
+    <t>G-054</t>
+  </si>
+  <si>
+    <t>VILLA KHE SANH</t>
+  </si>
+  <si>
+    <t>G-055</t>
+  </si>
+  <si>
+    <t>VILLA HOÀNG HOA THÁM</t>
+  </si>
+  <si>
+    <t>G-058</t>
+  </si>
+  <si>
+    <t>VILLA CARROT</t>
+  </si>
+  <si>
+    <t>G-060</t>
+  </si>
+  <si>
+    <t>VILLA BONJOUR 5</t>
+  </si>
+  <si>
     <t>G-062</t>
   </si>
   <si>
@@ -133,6 +379,72 @@
     <t>LA FOREST ĐÔI 302</t>
   </si>
   <si>
+    <t>G-067</t>
+  </si>
+  <si>
+    <t>LA FOREST ĐƠN 101</t>
+  </si>
+  <si>
+    <t>G-069</t>
+  </si>
+  <si>
+    <t>LA FOREST SUPERIOR 103</t>
+  </si>
+  <si>
+    <t>G-072</t>
+  </si>
+  <si>
+    <t>LA FOREST SUPERIOR 203</t>
+  </si>
+  <si>
+    <t>G-073</t>
+  </si>
+  <si>
+    <t>LA FOREST ĐƠN 301</t>
+  </si>
+  <si>
+    <t>G-076</t>
+  </si>
+  <si>
+    <t>LA FOREST ĐƠN 401</t>
+  </si>
+  <si>
+    <t>G-075</t>
+  </si>
+  <si>
+    <t>LA FOREST SUPERIOR 303</t>
+  </si>
+  <si>
+    <t>G-071</t>
+  </si>
+  <si>
+    <t>LA FOREST ĐÔI 202</t>
+  </si>
+  <si>
+    <t>G-077</t>
+  </si>
+  <si>
+    <t>LA FOREST ĐÔI 402</t>
+  </si>
+  <si>
+    <t>G-096</t>
+  </si>
+  <si>
+    <t>SONG NGƯ HOME</t>
+  </si>
+  <si>
+    <t>G-097</t>
+  </si>
+  <si>
+    <t>BẠCH DƯƠNG HOME</t>
+  </si>
+  <si>
+    <t>G-098</t>
+  </si>
+  <si>
+    <t>G VILLA</t>
+  </si>
+  <si>
     <t>G-078</t>
   </si>
   <si>
@@ -143,6 +455,135 @@
   </si>
   <si>
     <t>CASA HOME</t>
+  </si>
+  <si>
+    <t>G-086</t>
+  </si>
+  <si>
+    <t>VILLA BÁCH TÙNG VIÊN</t>
+  </si>
+  <si>
+    <t>KO NÂNG QUÁ 500K / ĐÊM</t>
+  </si>
+  <si>
+    <t>G-087</t>
+  </si>
+  <si>
+    <t>MIN VILLA</t>
+  </si>
+  <si>
+    <t>G-088</t>
+  </si>
+  <si>
+    <t>CHOPPER HOUSE</t>
+  </si>
+  <si>
+    <t>G-089</t>
+  </si>
+  <si>
+    <t>HOME 3 THÁNG 4</t>
+  </si>
+  <si>
+    <t>G-090</t>
+  </si>
+  <si>
+    <t>HALI VILLA</t>
+  </si>
+  <si>
+    <t>G-099</t>
+  </si>
+  <si>
+    <t>MOONDY HOUSE 1</t>
+  </si>
+  <si>
+    <t>CHÊNH =&lt; 1000K</t>
+  </si>
+  <si>
+    <t>G-100</t>
+  </si>
+  <si>
+    <t>MOONDY HOUSE 3</t>
+  </si>
+  <si>
+    <t>G-101</t>
+  </si>
+  <si>
+    <t>DENTRO HILL VILLA</t>
+  </si>
+  <si>
+    <t>G-102</t>
+  </si>
+  <si>
+    <t>FUHI'S HOUSE</t>
+  </si>
+  <si>
+    <t>G-103</t>
+  </si>
+  <si>
+    <t>ALBA HILL VILLA</t>
+  </si>
+  <si>
+    <t>G-104</t>
+  </si>
+  <si>
+    <t>GOLD VILLA</t>
+  </si>
+  <si>
+    <t>G-109</t>
+  </si>
+  <si>
+    <t>UT VILLA</t>
+  </si>
+  <si>
+    <t>CHÊNH TỐI ĐA 500K/ ĐÊM - Lễ tết chênh tối đa 1.000.000đ/ đêm</t>
+  </si>
+  <si>
+    <t>G-110</t>
+  </si>
+  <si>
+    <t>HBT HOME</t>
+  </si>
+  <si>
+    <t>G-111</t>
+  </si>
+  <si>
+    <t>NHÀ SÓC GẤU</t>
+  </si>
+  <si>
+    <t>G-112</t>
+  </si>
+  <si>
+    <t>TRỐN STAY</t>
+  </si>
+  <si>
+    <t>G-113</t>
+  </si>
+  <si>
+    <t>VIE'S HOME</t>
+  </si>
+  <si>
+    <t>G-114</t>
+  </si>
+  <si>
+    <t>CHƯƠNG'S HOUSE</t>
+  </si>
+  <si>
+    <t>G-115</t>
+  </si>
+  <si>
+    <t>VƯƠNG MÂY 1</t>
+  </si>
+  <si>
+    <t>G-116</t>
+  </si>
+  <si>
+    <t>VƯƠNG MÂY 2</t>
+  </si>
+  <si>
+    <t>G-117</t>
+  </si>
+  <si>
+    <t>VƯƠNG MÂY 3</t>
   </si>
 </sst>
 </file>
@@ -200,9 +641,9 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -542,7 +983,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N84"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -611,33 +1052,33 @@
         <v>15</v>
       </c>
       <c r="C2" s="2">
-        <v>1800000</v>
-      </c>
-      <c r="D2" s="3">
         <v>1600000</v>
       </c>
-      <c r="E2" s="4">
-        <v>2000000</v>
-      </c>
-      <c r="F2" s="4">
+      <c r="D2" s="2">
+        <v>1600000</v>
+      </c>
+      <c r="E2" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="F2" s="2">
         <v>2000000</v>
       </c>
       <c r="G2" s="2">
-        <v>300000</v>
-      </c>
-      <c r="H2" s="3">
         <v>500000</v>
       </c>
+      <c r="H2" s="2">
+        <v>500000</v>
+      </c>
       <c r="I2" s="2">
-        <v>600000</v>
-      </c>
-      <c r="J2" s="3">
         <v>1000000</v>
       </c>
-      <c r="K2" s="4">
+      <c r="J2" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="K2" s="2">
         <v>2100000</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="2">
         <v>2100000</v>
       </c>
       <c r="M2" t="s">
@@ -654,34 +1095,34 @@
       <c r="B3" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="4">
-        <v>2000000</v>
-      </c>
-      <c r="D3" s="4">
-        <v>2000000</v>
-      </c>
-      <c r="E3" s="2">
+      <c r="C3" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="D3" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="E3" s="3">
         <v>2500000</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="4">
         <v>2400000</v>
       </c>
       <c r="G3" s="2">
-        <v>400000</v>
-      </c>
-      <c r="H3" s="3">
         <v>500000</v>
       </c>
+      <c r="H3" s="2">
+        <v>500000</v>
+      </c>
       <c r="I3" s="2">
-        <v>800000</v>
-      </c>
-      <c r="J3" s="3">
         <v>1000000</v>
       </c>
-      <c r="K3" s="4">
-        <v>2400000</v>
-      </c>
-      <c r="L3" s="4">
+      <c r="J3" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="K3" s="2">
+        <v>2500000</v>
+      </c>
+      <c r="L3" s="2">
         <v>2500000</v>
       </c>
       <c r="M3" t="s">
@@ -699,31 +1140,31 @@
         <v>21</v>
       </c>
       <c r="C4" s="2">
-        <v>2000000</v>
-      </c>
-      <c r="D4" s="3">
         <v>1800000</v>
       </c>
+      <c r="D4" s="2">
+        <v>1800000</v>
+      </c>
       <c r="E4" s="2">
-        <v>2200000</v>
-      </c>
-      <c r="F4" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="F4" s="2">
         <v>2000000</v>
       </c>
       <c r="G4" s="2">
-        <v>400000</v>
-      </c>
-      <c r="H4" s="3">
         <v>500000</v>
       </c>
-      <c r="I4" s="4">
+      <c r="H4" s="2">
+        <v>500000</v>
+      </c>
+      <c r="I4" s="2">
         <v>800000</v>
       </c>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4">
-        <v>2400000</v>
-      </c>
-      <c r="L4" s="4">
+      <c r="J4" s="2"/>
+      <c r="K4" s="2">
+        <v>2300000</v>
+      </c>
+      <c r="L4" s="2">
         <v>2300000</v>
       </c>
       <c r="M4" t="s">
@@ -740,32 +1181,32 @@
       <c r="B5" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="2">
         <v>500000</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="2">
         <v>500000</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="2">
         <v>550000</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="2">
         <v>550000</v>
       </c>
       <c r="G5" s="2">
-        <v>150000</v>
-      </c>
-      <c r="H5" s="3">
         <v>500000</v>
       </c>
-      <c r="I5" s="4">
+      <c r="H5" s="2">
+        <v>500000</v>
+      </c>
+      <c r="I5" s="2">
         <v>300000</v>
       </c>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4">
-        <v>650000</v>
-      </c>
-      <c r="L5" s="4">
+      <c r="J5" s="2"/>
+      <c r="K5" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="L5" s="2">
         <v>1000000</v>
       </c>
       <c r="M5" t="s">
@@ -782,26 +1223,26 @@
       <c r="B6" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="2">
         <v>2200000</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4">
+      <c r="D6" s="2"/>
+      <c r="E6" s="2">
         <v>2500000</v>
       </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4">
+      <c r="F6" s="2"/>
+      <c r="G6" s="2">
         <v>400000</v>
       </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4">
+      <c r="H6" s="2"/>
+      <c r="I6" s="2">
         <v>800000</v>
       </c>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4">
+      <c r="J6" s="2"/>
+      <c r="K6" s="2">
         <v>2600000</v>
       </c>
-      <c r="L6" s="4">
+      <c r="L6" s="2">
         <v>2600000</v>
       </c>
       <c r="M6" t="s">
@@ -818,30 +1259,30 @@
       <c r="B7" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="4">
-        <v>2000000</v>
-      </c>
-      <c r="D7" s="4">
-        <v>2000000</v>
-      </c>
-      <c r="E7" s="2">
+      <c r="C7" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="D7" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="E7" s="3">
         <v>2300000</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="4">
         <v>2200000</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="2">
         <v>400000</v>
       </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4">
+      <c r="H7" s="2"/>
+      <c r="I7" s="2">
         <v>800000</v>
       </c>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4">
+      <c r="J7" s="2"/>
+      <c r="K7" s="2">
         <v>2400000</v>
       </c>
-      <c r="L7" s="4">
+      <c r="L7" s="2">
         <v>2400000</v>
       </c>
       <c r="M7" t="s">
@@ -858,63 +1299,63 @@
       <c r="B8" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="4">
-        <v>1700000</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4">
-        <v>2000000</v>
-      </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4">
-        <v>300000</v>
-      </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4">
-        <v>600000</v>
-      </c>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4">
-        <v>2000000</v>
-      </c>
-      <c r="L8" s="4">
-        <v>2000000</v>
+      <c r="C8" s="2">
+        <v>3000000</v>
+      </c>
+      <c r="D8" s="2">
+        <v>3000000</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2">
+        <v>4000000</v>
+      </c>
+      <c r="G8" s="2">
+        <v>400000</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2">
+        <v>3400000</v>
+      </c>
+      <c r="L8" s="2">
+        <v>3400000</v>
       </c>
       <c r="M8" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="N8" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="4">
-        <v>1500000</v>
-      </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4">
-        <v>1800000</v>
-      </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4">
-        <v>300000</v>
-      </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4">
-        <v>600000</v>
-      </c>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4">
-        <v>1800000</v>
-      </c>
-      <c r="L9" s="4">
-        <v>1800000</v>
+        <v>34</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2">
+        <v>2500000</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2">
+        <v>400000</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2">
+        <v>800000</v>
+      </c>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2">
+        <v>2400000</v>
+      </c>
+      <c r="L9" s="2">
+        <v>2400000</v>
       </c>
       <c r="M9" t="s">
         <v>17</v>
@@ -925,75 +1366,79 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="4">
-        <v>1500000</v>
-      </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4">
-        <v>1800000</v>
-      </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4">
-        <v>300000</v>
-      </c>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4">
-        <v>600000</v>
-      </c>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4">
-        <v>1800000</v>
-      </c>
-      <c r="L10" s="4">
-        <v>1800000</v>
+        <v>36</v>
+      </c>
+      <c r="C10" s="2">
+        <v>3500000</v>
+      </c>
+      <c r="D10" s="2">
+        <v>3500000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>4500000</v>
+      </c>
+      <c r="F10" s="4">
+        <v>4000000</v>
+      </c>
+      <c r="G10" s="2">
+        <v>500000</v>
+      </c>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2">
+        <v>4000000</v>
+      </c>
+      <c r="L10" s="2">
+        <v>4000000</v>
       </c>
       <c r="M10" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="N10" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="2">
+        <v>38</v>
+      </c>
+      <c r="C11" s="3">
+        <v>2500000</v>
+      </c>
+      <c r="D11" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="E11" s="3">
+        <v>3000000</v>
+      </c>
+      <c r="F11" s="4">
+        <v>2800000</v>
+      </c>
+      <c r="G11" s="2">
+        <v>400000</v>
+      </c>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2">
         <v>800000</v>
       </c>
-      <c r="D11" s="3">
-        <v>750000</v>
-      </c>
-      <c r="E11" s="2">
-        <v>800000</v>
-      </c>
-      <c r="F11" s="3">
-        <v>750000</v>
-      </c>
-      <c r="G11" s="4">
-        <v>150000</v>
-      </c>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4">
-        <v>300000</v>
-      </c>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4">
-        <v>950000</v>
-      </c>
-      <c r="L11" s="4">
-        <v>900000</v>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2">
+        <v>2900000</v>
+      </c>
+      <c r="L11" s="2">
+        <v>2400000</v>
       </c>
       <c r="M11" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="N11" t="s">
         <v>17</v>
@@ -1001,39 +1446,39 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C12" s="2">
+        <v>2500000</v>
+      </c>
+      <c r="D12" s="2">
+        <v>2500000</v>
+      </c>
+      <c r="E12" s="3">
+        <v>3500000</v>
+      </c>
+      <c r="F12" s="4">
+        <v>3000000</v>
+      </c>
+      <c r="G12" s="2">
+        <v>400000</v>
+      </c>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2">
         <v>800000</v>
       </c>
-      <c r="D12" s="3">
-        <v>750000</v>
-      </c>
-      <c r="E12" s="2">
-        <v>800000</v>
-      </c>
-      <c r="F12" s="3">
-        <v>750000</v>
-      </c>
-      <c r="G12" s="4">
-        <v>150000</v>
-      </c>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4">
-        <v>300000</v>
-      </c>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4">
-        <v>950000</v>
-      </c>
-      <c r="L12" s="4">
-        <v>900000</v>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2">
+        <v>2900000</v>
+      </c>
+      <c r="L12" s="2">
+        <v>2900000</v>
       </c>
       <c r="M12" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="N12" t="s">
         <v>17</v>
@@ -1041,32 +1486,32 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="4">
+        <v>42</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1600000</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2">
+        <v>1800000</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2">
         <v>600000</v>
       </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4">
-        <v>600000</v>
-      </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4">
-        <v>150000</v>
-      </c>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4">
-        <v>300000</v>
-      </c>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4">
-        <v>750000</v>
-      </c>
-      <c r="L13" s="4">
-        <v>750000</v>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2">
+        <v>1900000</v>
+      </c>
+      <c r="L13" s="2">
+        <v>1900000</v>
       </c>
       <c r="M13" t="s">
         <v>17</v>
@@ -1077,37 +1522,2805 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="4">
+        <v>44</v>
+      </c>
+      <c r="C14" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2">
+        <v>2400000</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2">
+        <v>400000</v>
+      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2">
+        <v>800000</v>
+      </c>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2">
+        <v>2400000</v>
+      </c>
+      <c r="L14" s="2">
+        <v>2400000</v>
+      </c>
+      <c r="M14" t="s">
+        <v>17</v>
+      </c>
+      <c r="N14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="2">
+        <v>1600000</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1600000</v>
+      </c>
+      <c r="E15" s="2">
+        <v>2200000</v>
+      </c>
+      <c r="F15" s="2">
+        <v>2200000</v>
+      </c>
+      <c r="G15" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2">
+        <v>600000</v>
+      </c>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2">
+        <v>1900000</v>
+      </c>
+      <c r="L15" s="2">
+        <v>1900000</v>
+      </c>
+      <c r="M15" t="s">
+        <v>32</v>
+      </c>
+      <c r="N15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1300000</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1300000</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1800000</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1800000</v>
+      </c>
+      <c r="G16" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2">
+        <v>600000</v>
+      </c>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2">
+        <v>1600000</v>
+      </c>
+      <c r="L16" s="2">
+        <v>1600000</v>
+      </c>
+      <c r="M16" t="s">
+        <v>32</v>
+      </c>
+      <c r="N16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="3">
+        <v>2300000</v>
+      </c>
+      <c r="D17" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2800000</v>
+      </c>
+      <c r="F17" s="4">
+        <v>2500000</v>
+      </c>
+      <c r="G17" s="2">
+        <v>400000</v>
+      </c>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2">
+        <v>800000</v>
+      </c>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2">
+        <v>2700000</v>
+      </c>
+      <c r="L17" s="2">
+        <v>2400000</v>
+      </c>
+      <c r="M17" t="s">
+        <v>32</v>
+      </c>
+      <c r="N17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="2">
+        <v>3000000</v>
+      </c>
+      <c r="D18" s="2">
+        <v>3000000</v>
+      </c>
+      <c r="E18" s="2">
+        <v>3500000</v>
+      </c>
+      <c r="F18" s="2">
+        <v>3500000</v>
+      </c>
+      <c r="G18" s="2">
+        <v>400000</v>
+      </c>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2">
+        <v>800000</v>
+      </c>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2">
+        <v>3400000</v>
+      </c>
+      <c r="L18" s="2">
+        <v>3400000</v>
+      </c>
+      <c r="M18" t="s">
+        <v>32</v>
+      </c>
+      <c r="N18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1500000</v>
+      </c>
+      <c r="D19" s="2">
+        <v>1500000</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1800000</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1800000</v>
+      </c>
+      <c r="G19" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2">
+        <v>600000</v>
+      </c>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2">
+        <v>1800000</v>
+      </c>
+      <c r="L19" s="2">
+        <v>1800000</v>
+      </c>
+      <c r="M19" t="s">
+        <v>32</v>
+      </c>
+      <c r="N19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" s="3">
+        <v>1500000</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1200000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="F20" s="4">
+        <v>1200000</v>
+      </c>
+      <c r="G20" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2">
+        <v>600000</v>
+      </c>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2">
+        <v>1800000</v>
+      </c>
+      <c r="L20" s="2">
+        <v>1500000</v>
+      </c>
+      <c r="M20" t="s">
+        <v>32</v>
+      </c>
+      <c r="N20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" s="3">
+        <v>1100000</v>
+      </c>
+      <c r="D21" s="4">
+        <v>1200000</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1300000</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1300000</v>
+      </c>
+      <c r="G21" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2">
+        <v>600000</v>
+      </c>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2">
+        <v>1400000</v>
+      </c>
+      <c r="L21" s="2">
+        <v>1500000</v>
+      </c>
+      <c r="M21" t="s">
+        <v>32</v>
+      </c>
+      <c r="N21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="3">
+        <v>1100000</v>
+      </c>
+      <c r="D22" s="4">
+        <v>1000000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1300000</v>
+      </c>
+      <c r="F22" s="4">
+        <v>1100000</v>
+      </c>
+      <c r="G22" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2">
+        <v>600000</v>
+      </c>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2">
+        <v>1400000</v>
+      </c>
+      <c r="L22" s="2">
+        <v>1300000</v>
+      </c>
+      <c r="M22" t="s">
+        <v>32</v>
+      </c>
+      <c r="N22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="3">
+        <v>400000</v>
+      </c>
+      <c r="D23" s="4">
+        <v>300000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>500000</v>
+      </c>
+      <c r="F23" s="4">
+        <v>300000</v>
+      </c>
+      <c r="G23" s="2">
+        <v>150000</v>
+      </c>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2">
+        <v>300000</v>
+      </c>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2">
+        <v>550000</v>
+      </c>
+      <c r="L23" s="2">
+        <v>450000</v>
+      </c>
+      <c r="M23" t="s">
+        <v>32</v>
+      </c>
+      <c r="N23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="2">
+        <v>600000</v>
+      </c>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2">
+        <v>600000</v>
+      </c>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2">
+        <v>150000</v>
+      </c>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2">
+        <v>300000</v>
+      </c>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2">
+        <v>750000</v>
+      </c>
+      <c r="L24" s="2">
+        <v>750000</v>
+      </c>
+      <c r="M24" t="s">
+        <v>17</v>
+      </c>
+      <c r="N24" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" s="2">
+        <v>800000</v>
+      </c>
+      <c r="D25" s="2">
+        <v>800000</v>
+      </c>
+      <c r="E25" s="3">
+        <v>900000</v>
+      </c>
+      <c r="F25" s="4">
+        <v>1000000</v>
+      </c>
+      <c r="G25" s="2">
+        <v>150000</v>
+      </c>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2">
+        <v>950000</v>
+      </c>
+      <c r="L25" s="2">
+        <v>950000</v>
+      </c>
+      <c r="M25" t="s">
+        <v>32</v>
+      </c>
+      <c r="N25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" s="2">
+        <v>3000000</v>
+      </c>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2">
         <v>4000000</v>
       </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4">
+      <c r="F26" s="2"/>
+      <c r="G26" s="2">
+        <v>400000</v>
+      </c>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2">
+        <v>800000</v>
+      </c>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2">
+        <v>3400000</v>
+      </c>
+      <c r="L26" s="2">
+        <v>3400000</v>
+      </c>
+      <c r="M26" t="s">
+        <v>17</v>
+      </c>
+      <c r="N26" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>69</v>
+      </c>
+      <c r="B27" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" s="2">
+        <v>2700000</v>
+      </c>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2">
+        <v>3500000</v>
+      </c>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2">
+        <v>400000</v>
+      </c>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2">
+        <v>800000</v>
+      </c>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="L27" s="2">
+        <v>3100000</v>
+      </c>
+      <c r="M27" t="s">
+        <v>17</v>
+      </c>
+      <c r="N27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>71</v>
+      </c>
+      <c r="B28" t="s">
+        <v>72</v>
+      </c>
+      <c r="C28" s="2">
+        <v>2800000</v>
+      </c>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2">
+        <v>3000000</v>
+      </c>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2">
+        <v>400000</v>
+      </c>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2">
+        <v>800000</v>
+      </c>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2">
+        <v>3200000</v>
+      </c>
+      <c r="L28" s="2">
+        <v>3200000</v>
+      </c>
+      <c r="M28" t="s">
+        <v>17</v>
+      </c>
+      <c r="N28" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>73</v>
+      </c>
+      <c r="B29" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2">
+        <v>400000</v>
+      </c>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2">
+        <v>800000</v>
+      </c>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2">
+        <v>2400000</v>
+      </c>
+      <c r="L29" s="2">
+        <v>2400000</v>
+      </c>
+      <c r="M29" t="s">
+        <v>17</v>
+      </c>
+      <c r="N29" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>75</v>
+      </c>
+      <c r="B30" t="s">
+        <v>76</v>
+      </c>
+      <c r="C30" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="D30" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="E30" s="2">
+        <v>2500000</v>
+      </c>
+      <c r="F30" s="2">
+        <v>2500000</v>
+      </c>
+      <c r="G30" s="3">
+        <v>400000</v>
+      </c>
+      <c r="H30" s="4">
+        <v>500000</v>
+      </c>
+      <c r="I30" s="3">
+        <v>800000</v>
+      </c>
+      <c r="J30" s="4">
+        <v>1000000</v>
+      </c>
+      <c r="K30" s="2">
+        <v>2400000</v>
+      </c>
+      <c r="L30" s="2">
+        <v>2500000</v>
+      </c>
+      <c r="M30" t="s">
+        <v>77</v>
+      </c>
+      <c r="N30" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>78</v>
+      </c>
+      <c r="B31" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2">
+        <v>400000</v>
+      </c>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2">
+        <v>800000</v>
+      </c>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2">
+        <v>2400000</v>
+      </c>
+      <c r="L31" s="2">
+        <v>2400000</v>
+      </c>
+      <c r="M31" t="s">
+        <v>17</v>
+      </c>
+      <c r="N31" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>80</v>
+      </c>
+      <c r="B32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" s="2">
+        <v>1200000</v>
+      </c>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2">
+        <v>1500000</v>
+      </c>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2">
+        <v>600000</v>
+      </c>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2">
+        <v>1500000</v>
+      </c>
+      <c r="L32" s="2">
+        <v>1500000</v>
+      </c>
+      <c r="M32" t="s">
+        <v>17</v>
+      </c>
+      <c r="N32" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33" t="s">
+        <v>83</v>
+      </c>
+      <c r="C33" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="D33" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>2500000</v>
+      </c>
+      <c r="F33" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="G33" s="3">
+        <v>400000</v>
+      </c>
+      <c r="H33" s="4">
+        <v>200000</v>
+      </c>
+      <c r="I33" s="2">
+        <v>800000</v>
+      </c>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2">
+        <v>2400000</v>
+      </c>
+      <c r="L33" s="2">
+        <v>2200000</v>
+      </c>
+      <c r="M33" t="s">
+        <v>84</v>
+      </c>
+      <c r="N33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>85</v>
+      </c>
+      <c r="B34" t="s">
+        <v>86</v>
+      </c>
+      <c r="C34" s="2">
+        <v>1500000</v>
+      </c>
+      <c r="D34" s="2">
+        <v>1500000</v>
+      </c>
+      <c r="E34" s="2">
+        <v>1800000</v>
+      </c>
+      <c r="F34" s="2">
+        <v>1800000</v>
+      </c>
+      <c r="G34" s="3">
+        <v>300000</v>
+      </c>
+      <c r="H34" s="4">
+        <v>200000</v>
+      </c>
+      <c r="I34" s="2">
+        <v>600000</v>
+      </c>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2">
+        <v>1800000</v>
+      </c>
+      <c r="L34" s="2">
+        <v>1700000</v>
+      </c>
+      <c r="M34" t="s">
+        <v>84</v>
+      </c>
+      <c r="N34" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>87</v>
+      </c>
+      <c r="B35" t="s">
+        <v>88</v>
+      </c>
+      <c r="C35" s="2">
+        <v>4000000</v>
+      </c>
+      <c r="D35" s="2">
+        <v>4000000</v>
+      </c>
+      <c r="E35" s="2">
         <v>4500000</v>
       </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4">
+      <c r="F35" s="2">
+        <v>4500000</v>
+      </c>
+      <c r="G35" s="3">
         <v>500000</v>
       </c>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4">
+      <c r="H35" s="4">
+        <v>200000</v>
+      </c>
+      <c r="I35" s="2">
         <v>1000000</v>
       </c>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4">
+      <c r="J35" s="2"/>
+      <c r="K35" s="2">
         <v>4500000</v>
       </c>
-      <c r="L14" s="4">
+      <c r="L35" s="2">
+        <v>4200000</v>
+      </c>
+      <c r="M35" t="s">
+        <v>84</v>
+      </c>
+      <c r="N35" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>89</v>
+      </c>
+      <c r="B36" t="s">
+        <v>90</v>
+      </c>
+      <c r="C36" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2">
+        <v>2200000</v>
+      </c>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2">
+        <v>400000</v>
+      </c>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2">
+        <v>800000</v>
+      </c>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2">
+        <v>2400000</v>
+      </c>
+      <c r="L36" s="2">
+        <v>2400000</v>
+      </c>
+      <c r="M36" t="s">
+        <v>17</v>
+      </c>
+      <c r="N36" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>91</v>
+      </c>
+      <c r="B37" t="s">
+        <v>92</v>
+      </c>
+      <c r="C37" s="2">
+        <v>1500000</v>
+      </c>
+      <c r="D37" s="2">
+        <v>1500000</v>
+      </c>
+      <c r="E37" s="3">
+        <v>1800000</v>
+      </c>
+      <c r="F37" s="4">
+        <v>1600000</v>
+      </c>
+      <c r="G37" s="3">
+        <v>300000</v>
+      </c>
+      <c r="H37" s="4">
+        <v>200000</v>
+      </c>
+      <c r="I37" s="2">
+        <v>600000</v>
+      </c>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2">
+        <v>1800000</v>
+      </c>
+      <c r="L37" s="2">
+        <v>1700000</v>
+      </c>
+      <c r="M37" t="s">
+        <v>84</v>
+      </c>
+      <c r="N37" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>93</v>
+      </c>
+      <c r="B38" t="s">
+        <v>94</v>
+      </c>
+      <c r="C38" s="2">
         <v>4500000</v>
       </c>
-      <c r="M14" t="s">
-        <v>17</v>
-      </c>
-      <c r="N14" t="s">
+      <c r="D38" s="2"/>
+      <c r="E38" s="2">
+        <v>5500000</v>
+      </c>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2">
+        <v>500000</v>
+      </c>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2">
+        <v>5000000</v>
+      </c>
+      <c r="L38" s="2">
+        <v>5000000</v>
+      </c>
+      <c r="M38" t="s">
+        <v>17</v>
+      </c>
+      <c r="N38" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>95</v>
+      </c>
+      <c r="B39" t="s">
+        <v>96</v>
+      </c>
+      <c r="C39" s="3">
+        <v>2500000</v>
+      </c>
+      <c r="D39" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="E39" s="2">
+        <v>3000000</v>
+      </c>
+      <c r="F39" s="2"/>
+      <c r="G39" s="3">
+        <v>400000</v>
+      </c>
+      <c r="H39" s="4">
+        <v>700000</v>
+      </c>
+      <c r="I39" s="3">
+        <v>800000</v>
+      </c>
+      <c r="J39" s="4">
+        <v>1000000</v>
+      </c>
+      <c r="K39" s="2">
+        <v>2900000</v>
+      </c>
+      <c r="L39" s="2">
+        <v>2700000</v>
+      </c>
+      <c r="M39" t="s">
+        <v>97</v>
+      </c>
+      <c r="N39" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>98</v>
+      </c>
+      <c r="B40" t="s">
+        <v>99</v>
+      </c>
+      <c r="C40" s="3">
+        <v>4000000</v>
+      </c>
+      <c r="D40" s="4">
+        <v>3200000</v>
+      </c>
+      <c r="E40" s="2">
+        <v>4500000</v>
+      </c>
+      <c r="F40" s="2"/>
+      <c r="G40" s="3">
+        <v>500000</v>
+      </c>
+      <c r="H40" s="4">
+        <v>700000</v>
+      </c>
+      <c r="I40" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="J40" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="K40" s="2">
+        <v>4500000</v>
+      </c>
+      <c r="L40" s="2">
+        <v>3900000</v>
+      </c>
+      <c r="M40" t="s">
+        <v>97</v>
+      </c>
+      <c r="N40" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>100</v>
+      </c>
+      <c r="B41" t="s">
+        <v>101</v>
+      </c>
+      <c r="C41" s="2">
+        <v>2500000</v>
+      </c>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2">
+        <v>3000000</v>
+      </c>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2">
+        <v>400000</v>
+      </c>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2">
+        <v>800000</v>
+      </c>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2">
+        <v>2900000</v>
+      </c>
+      <c r="L41" s="2">
+        <v>2900000</v>
+      </c>
+      <c r="M41" t="s">
+        <v>17</v>
+      </c>
+      <c r="N41" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>102</v>
+      </c>
+      <c r="B42" t="s">
+        <v>103</v>
+      </c>
+      <c r="C42" s="2">
+        <v>2500000</v>
+      </c>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2">
+        <v>3000000</v>
+      </c>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2">
+        <v>400000</v>
+      </c>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2">
+        <v>800000</v>
+      </c>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2">
+        <v>2900000</v>
+      </c>
+      <c r="L42" s="2">
+        <v>2900000</v>
+      </c>
+      <c r="M42" t="s">
+        <v>17</v>
+      </c>
+      <c r="N42" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>104</v>
+      </c>
+      <c r="B43" t="s">
+        <v>105</v>
+      </c>
+      <c r="C43" s="2">
+        <v>2500000</v>
+      </c>
+      <c r="D43" s="2">
+        <v>2500000</v>
+      </c>
+      <c r="E43" s="2">
+        <v>3000000</v>
+      </c>
+      <c r="F43" s="2">
+        <v>3000000</v>
+      </c>
+      <c r="G43" s="2">
+        <v>400000</v>
+      </c>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2">
+        <v>800000</v>
+      </c>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2">
+        <v>2900000</v>
+      </c>
+      <c r="L43" s="2">
+        <v>2900000</v>
+      </c>
+      <c r="M43" t="s">
+        <v>17</v>
+      </c>
+      <c r="N43" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>106</v>
+      </c>
+      <c r="B44" t="s">
+        <v>107</v>
+      </c>
+      <c r="C44" s="3">
+        <v>1700000</v>
+      </c>
+      <c r="D44" s="4">
+        <v>1500000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2200000</v>
+      </c>
+      <c r="F44" s="4">
+        <v>2500000</v>
+      </c>
+      <c r="G44" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2">
+        <v>600000</v>
+      </c>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="L44" s="2">
+        <v>1800000</v>
+      </c>
+      <c r="M44" t="s">
+        <v>17</v>
+      </c>
+      <c r="N44" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>108</v>
+      </c>
+      <c r="B45" t="s">
+        <v>109</v>
+      </c>
+      <c r="C45" s="2">
+        <v>2800000</v>
+      </c>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2">
+        <v>3800000</v>
+      </c>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2">
+        <v>400000</v>
+      </c>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2">
+        <v>800000</v>
+      </c>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2">
+        <v>3200000</v>
+      </c>
+      <c r="L45" s="2">
+        <v>3200000</v>
+      </c>
+      <c r="M45" t="s">
+        <v>17</v>
+      </c>
+      <c r="N45" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>110</v>
+      </c>
+      <c r="B46" t="s">
+        <v>111</v>
+      </c>
+      <c r="C46" s="2">
+        <v>3000000</v>
+      </c>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2">
+        <v>3000000</v>
+      </c>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2">
+        <v>400000</v>
+      </c>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2">
+        <v>800000</v>
+      </c>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2">
+        <v>3400000</v>
+      </c>
+      <c r="L46" s="2">
+        <v>3400000</v>
+      </c>
+      <c r="M46" t="s">
+        <v>17</v>
+      </c>
+      <c r="N46" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>112</v>
+      </c>
+      <c r="B47" t="s">
+        <v>113</v>
+      </c>
+      <c r="C47" s="2">
+        <v>1700000</v>
+      </c>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2">
+        <v>600000</v>
+      </c>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="L47" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="M47" t="s">
+        <v>17</v>
+      </c>
+      <c r="N47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>114</v>
+      </c>
+      <c r="B48" t="s">
+        <v>115</v>
+      </c>
+      <c r="C48" s="2">
+        <v>1500000</v>
+      </c>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2">
+        <v>1800000</v>
+      </c>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2">
+        <v>600000</v>
+      </c>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2">
+        <v>1800000</v>
+      </c>
+      <c r="L48" s="2">
+        <v>1800000</v>
+      </c>
+      <c r="M48" t="s">
+        <v>17</v>
+      </c>
+      <c r="N48" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>116</v>
+      </c>
+      <c r="B49" t="s">
+        <v>117</v>
+      </c>
+      <c r="C49" s="2">
+        <v>1500000</v>
+      </c>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2">
+        <v>1800000</v>
+      </c>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2">
+        <v>600000</v>
+      </c>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2">
+        <v>1800000</v>
+      </c>
+      <c r="L49" s="2">
+        <v>1800000</v>
+      </c>
+      <c r="M49" t="s">
+        <v>17</v>
+      </c>
+      <c r="N49" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>118</v>
+      </c>
+      <c r="B50" t="s">
+        <v>119</v>
+      </c>
+      <c r="C50" s="2">
+        <v>750000</v>
+      </c>
+      <c r="D50" s="2">
+        <v>750000</v>
+      </c>
+      <c r="E50" s="2">
+        <v>750000</v>
+      </c>
+      <c r="F50" s="2">
+        <v>750000</v>
+      </c>
+      <c r="G50" s="2">
+        <v>150000</v>
+      </c>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2">
+        <v>300000</v>
+      </c>
+      <c r="J50" s="2"/>
+      <c r="K50" s="2">
+        <v>900000</v>
+      </c>
+      <c r="L50" s="2">
+        <v>900000</v>
+      </c>
+      <c r="M50" t="s">
+        <v>17</v>
+      </c>
+      <c r="N50" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>120</v>
+      </c>
+      <c r="B51" t="s">
+        <v>121</v>
+      </c>
+      <c r="C51" s="2">
+        <v>750000</v>
+      </c>
+      <c r="D51" s="2">
+        <v>750000</v>
+      </c>
+      <c r="E51" s="2">
+        <v>750000</v>
+      </c>
+      <c r="F51" s="2">
+        <v>750000</v>
+      </c>
+      <c r="G51" s="2">
+        <v>150000</v>
+      </c>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2">
+        <v>300000</v>
+      </c>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2">
+        <v>900000</v>
+      </c>
+      <c r="L51" s="2">
+        <v>900000</v>
+      </c>
+      <c r="M51" t="s">
+        <v>17</v>
+      </c>
+      <c r="N51" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>122</v>
+      </c>
+      <c r="B52" t="s">
+        <v>123</v>
+      </c>
+      <c r="C52" s="2">
+        <v>700000</v>
+      </c>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2">
+        <v>700000</v>
+      </c>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2">
+        <v>150000</v>
+      </c>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2">
+        <v>300000</v>
+      </c>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2">
+        <v>850000</v>
+      </c>
+      <c r="L52" s="2">
+        <v>850000</v>
+      </c>
+      <c r="M52" t="s">
+        <v>17</v>
+      </c>
+      <c r="N52" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>124</v>
+      </c>
+      <c r="B53" t="s">
+        <v>125</v>
+      </c>
+      <c r="C53" s="2">
+        <v>600000</v>
+      </c>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2">
+        <v>600000</v>
+      </c>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2">
+        <v>150000</v>
+      </c>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2">
+        <v>300000</v>
+      </c>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2">
+        <v>750000</v>
+      </c>
+      <c r="L53" s="2">
+        <v>750000</v>
+      </c>
+      <c r="M53" t="s">
+        <v>17</v>
+      </c>
+      <c r="N53" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>126</v>
+      </c>
+      <c r="B54" t="s">
+        <v>127</v>
+      </c>
+      <c r="C54" s="2">
+        <v>600000</v>
+      </c>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2">
+        <v>600000</v>
+      </c>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2">
+        <v>150000</v>
+      </c>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2">
+        <v>300000</v>
+      </c>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2">
+        <v>750000</v>
+      </c>
+      <c r="L54" s="2">
+        <v>750000</v>
+      </c>
+      <c r="M54" t="s">
+        <v>17</v>
+      </c>
+      <c r="N54" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>128</v>
+      </c>
+      <c r="B55" t="s">
+        <v>129</v>
+      </c>
+      <c r="C55" s="2">
+        <v>550000</v>
+      </c>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2">
+        <v>550000</v>
+      </c>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2">
+        <v>150000</v>
+      </c>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2">
+        <v>300000</v>
+      </c>
+      <c r="J55" s="2"/>
+      <c r="K55" s="2">
+        <v>700000</v>
+      </c>
+      <c r="L55" s="2">
+        <v>700000</v>
+      </c>
+      <c r="M55" t="s">
+        <v>17</v>
+      </c>
+      <c r="N55" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>130</v>
+      </c>
+      <c r="B56" t="s">
+        <v>131</v>
+      </c>
+      <c r="C56" s="2">
+        <v>550000</v>
+      </c>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2">
+        <v>550000</v>
+      </c>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2">
+        <v>150000</v>
+      </c>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2">
+        <v>300000</v>
+      </c>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2">
+        <v>700000</v>
+      </c>
+      <c r="L56" s="2">
+        <v>700000</v>
+      </c>
+      <c r="M56" t="s">
+        <v>17</v>
+      </c>
+      <c r="N56" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>132</v>
+      </c>
+      <c r="B57" t="s">
+        <v>133</v>
+      </c>
+      <c r="C57" s="2">
+        <v>600000</v>
+      </c>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2">
+        <v>600000</v>
+      </c>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2">
+        <v>150000</v>
+      </c>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2">
+        <v>300000</v>
+      </c>
+      <c r="J57" s="2"/>
+      <c r="K57" s="2">
+        <v>750000</v>
+      </c>
+      <c r="L57" s="2">
+        <v>750000</v>
+      </c>
+      <c r="M57" t="s">
+        <v>17</v>
+      </c>
+      <c r="N57" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>134</v>
+      </c>
+      <c r="B58" t="s">
+        <v>135</v>
+      </c>
+      <c r="C58" s="2">
+        <v>800000</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2">
+        <v>800000</v>
+      </c>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2">
+        <v>150000</v>
+      </c>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2">
+        <v>300000</v>
+      </c>
+      <c r="J58" s="2"/>
+      <c r="K58" s="2">
+        <v>950000</v>
+      </c>
+      <c r="L58" s="2">
+        <v>950000</v>
+      </c>
+      <c r="M58" t="s">
+        <v>17</v>
+      </c>
+      <c r="N58" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>136</v>
+      </c>
+      <c r="B59" t="s">
+        <v>137</v>
+      </c>
+      <c r="C59" s="2">
+        <v>800000</v>
+      </c>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2">
+        <v>800000</v>
+      </c>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2">
+        <v>150000</v>
+      </c>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2">
+        <v>300000</v>
+      </c>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2">
+        <v>950000</v>
+      </c>
+      <c r="L59" s="2">
+        <v>950000</v>
+      </c>
+      <c r="M59" t="s">
+        <v>17</v>
+      </c>
+      <c r="N59" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>138</v>
+      </c>
+      <c r="B60" t="s">
+        <v>139</v>
+      </c>
+      <c r="C60" s="3">
+        <v>1200000</v>
+      </c>
+      <c r="D60" s="4">
+        <v>800000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1800000</v>
+      </c>
+      <c r="F60" s="4">
+        <v>1000000</v>
+      </c>
+      <c r="G60" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2">
+        <v>600000</v>
+      </c>
+      <c r="J60" s="2"/>
+      <c r="K60" s="2">
+        <v>1500000</v>
+      </c>
+      <c r="L60" s="2">
+        <v>1100000</v>
+      </c>
+      <c r="M60" t="s">
+        <v>17</v>
+      </c>
+      <c r="N60" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>140</v>
+      </c>
+      <c r="B61" t="s">
+        <v>141</v>
+      </c>
+      <c r="C61" s="2">
+        <v>1500000</v>
+      </c>
+      <c r="D61" s="2">
+        <v>1500000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1800000</v>
+      </c>
+      <c r="F61" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="G61" s="2">
+        <v>300000</v>
+      </c>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2">
+        <v>600000</v>
+      </c>
+      <c r="J61" s="2"/>
+      <c r="K61" s="2">
+        <v>1800000</v>
+      </c>
+      <c r="L61" s="2">
+        <v>1800000</v>
+      </c>
+      <c r="M61" t="s">
+        <v>17</v>
+      </c>
+      <c r="N61" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>142</v>
+      </c>
+      <c r="B62" t="s">
+        <v>143</v>
+      </c>
+      <c r="C62" s="3">
+        <v>4000000</v>
+      </c>
+      <c r="D62" s="4">
+        <v>3000000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>5000000</v>
+      </c>
+      <c r="F62" s="4">
+        <v>4000000</v>
+      </c>
+      <c r="G62" s="2">
+        <v>500000</v>
+      </c>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2">
+        <v>4500000</v>
+      </c>
+      <c r="L62" s="2">
+        <v>3500000</v>
+      </c>
+      <c r="M62" t="s">
+        <v>17</v>
+      </c>
+      <c r="N62" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>144</v>
+      </c>
+      <c r="B63" t="s">
+        <v>145</v>
+      </c>
+      <c r="C63" s="2">
+        <v>600000</v>
+      </c>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2">
+        <v>600000</v>
+      </c>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2">
+        <v>150000</v>
+      </c>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2">
+        <v>300000</v>
+      </c>
+      <c r="J63" s="2"/>
+      <c r="K63" s="2">
+        <v>750000</v>
+      </c>
+      <c r="L63" s="2">
+        <v>750000</v>
+      </c>
+      <c r="M63" t="s">
+        <v>17</v>
+      </c>
+      <c r="N63" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>146</v>
+      </c>
+      <c r="B64" t="s">
+        <v>147</v>
+      </c>
+      <c r="C64" s="2">
+        <v>4000000</v>
+      </c>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2">
+        <v>4500000</v>
+      </c>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2">
+        <v>500000</v>
+      </c>
+      <c r="H64" s="2"/>
+      <c r="I64" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="J64" s="2"/>
+      <c r="K64" s="2">
+        <v>4500000</v>
+      </c>
+      <c r="L64" s="2">
+        <v>4500000</v>
+      </c>
+      <c r="M64" t="s">
+        <v>17</v>
+      </c>
+      <c r="N64" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>148</v>
+      </c>
+      <c r="B65" t="s">
+        <v>149</v>
+      </c>
+      <c r="C65" s="2">
+        <v>4500000</v>
+      </c>
+      <c r="D65" s="2">
+        <v>4500000</v>
+      </c>
+      <c r="E65" s="2">
+        <v>5000000</v>
+      </c>
+      <c r="F65" s="2">
+        <v>5000000</v>
+      </c>
+      <c r="G65" s="2">
+        <v>500000</v>
+      </c>
+      <c r="H65" s="2">
+        <v>500000</v>
+      </c>
+      <c r="I65" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="J65" s="2"/>
+      <c r="K65" s="2">
+        <v>5000000</v>
+      </c>
+      <c r="L65" s="2">
+        <v>5000000</v>
+      </c>
+      <c r="M65" t="s">
+        <v>150</v>
+      </c>
+      <c r="N65" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>151</v>
+      </c>
+      <c r="B66" t="s">
+        <v>152</v>
+      </c>
+      <c r="C66" s="2">
+        <v>3500000</v>
+      </c>
+      <c r="D66" s="2">
+        <v>3500000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>4000000</v>
+      </c>
+      <c r="F66" s="4">
+        <v>3500000</v>
+      </c>
+      <c r="G66" s="2">
+        <v>500000</v>
+      </c>
+      <c r="H66" s="2">
+        <v>500000</v>
+      </c>
+      <c r="I66" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="J66" s="2"/>
+      <c r="K66" s="2">
+        <v>4000000</v>
+      </c>
+      <c r="L66" s="2">
+        <v>4000000</v>
+      </c>
+      <c r="M66" t="s">
+        <v>150</v>
+      </c>
+      <c r="N66" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>153</v>
+      </c>
+      <c r="B67" t="s">
+        <v>154</v>
+      </c>
+      <c r="C67" s="3">
+        <v>1800000</v>
+      </c>
+      <c r="D67" s="4">
+        <v>1500000</v>
+      </c>
+      <c r="E67" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="F67" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="G67" s="3">
+        <v>300000</v>
+      </c>
+      <c r="H67" s="4">
+        <v>500000</v>
+      </c>
+      <c r="I67" s="2">
+        <v>600000</v>
+      </c>
+      <c r="J67" s="2"/>
+      <c r="K67" s="2">
+        <v>2100000</v>
+      </c>
+      <c r="L67" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="M67" t="s">
+        <v>150</v>
+      </c>
+      <c r="N67" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>155</v>
+      </c>
+      <c r="B68" t="s">
+        <v>156</v>
+      </c>
+      <c r="C68" s="3">
+        <v>1800000</v>
+      </c>
+      <c r="D68" s="4">
+        <v>1500000</v>
+      </c>
+      <c r="E68" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="F68" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="G68" s="3">
+        <v>300000</v>
+      </c>
+      <c r="H68" s="4">
+        <v>500000</v>
+      </c>
+      <c r="I68" s="2">
+        <v>600000</v>
+      </c>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2">
+        <v>2100000</v>
+      </c>
+      <c r="L68" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="M68" t="s">
+        <v>150</v>
+      </c>
+      <c r="N68" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>157</v>
+      </c>
+      <c r="B69" t="s">
+        <v>158</v>
+      </c>
+      <c r="C69" s="3">
+        <v>3000000</v>
+      </c>
+      <c r="D69" s="4">
+        <v>2300000</v>
+      </c>
+      <c r="E69" s="3">
+        <v>3500000</v>
+      </c>
+      <c r="F69" s="4">
+        <v>3000000</v>
+      </c>
+      <c r="G69" s="3">
+        <v>400000</v>
+      </c>
+      <c r="H69" s="4">
+        <v>500000</v>
+      </c>
+      <c r="I69" s="2">
+        <v>800000</v>
+      </c>
+      <c r="J69" s="2"/>
+      <c r="K69" s="2">
+        <v>3400000</v>
+      </c>
+      <c r="L69" s="2">
+        <v>2800000</v>
+      </c>
+      <c r="M69" t="s">
+        <v>150</v>
+      </c>
+      <c r="N69" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>159</v>
+      </c>
+      <c r="B70" t="s">
+        <v>160</v>
+      </c>
+      <c r="C70" s="2">
+        <v>1200000</v>
+      </c>
+      <c r="D70" s="2">
+        <v>1200000</v>
+      </c>
+      <c r="E70" s="2">
+        <v>1400000</v>
+      </c>
+      <c r="F70" s="2">
+        <v>1400000</v>
+      </c>
+      <c r="G70" s="3">
+        <v>300000</v>
+      </c>
+      <c r="H70" s="4">
+        <v>1000000</v>
+      </c>
+      <c r="I70" s="2">
+        <v>600000</v>
+      </c>
+      <c r="J70" s="2"/>
+      <c r="K70" s="2">
+        <v>1500000</v>
+      </c>
+      <c r="L70" s="2">
+        <v>2200000</v>
+      </c>
+      <c r="M70" t="s">
+        <v>161</v>
+      </c>
+      <c r="N70" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>162</v>
+      </c>
+      <c r="B71" t="s">
+        <v>163</v>
+      </c>
+      <c r="C71" s="2">
+        <v>1200000</v>
+      </c>
+      <c r="D71" s="2">
+        <v>1200000</v>
+      </c>
+      <c r="E71" s="2">
+        <v>1400000</v>
+      </c>
+      <c r="F71" s="2">
+        <v>1400000</v>
+      </c>
+      <c r="G71" s="3">
+        <v>300000</v>
+      </c>
+      <c r="H71" s="4">
+        <v>1000000</v>
+      </c>
+      <c r="I71" s="2">
+        <v>600000</v>
+      </c>
+      <c r="J71" s="2"/>
+      <c r="K71" s="2">
+        <v>1500000</v>
+      </c>
+      <c r="L71" s="2">
+        <v>2200000</v>
+      </c>
+      <c r="M71" t="s">
+        <v>161</v>
+      </c>
+      <c r="N71" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>164</v>
+      </c>
+      <c r="B72" t="s">
+        <v>165</v>
+      </c>
+      <c r="C72" s="2">
+        <v>1600000</v>
+      </c>
+      <c r="D72" s="2">
+        <v>1600000</v>
+      </c>
+      <c r="E72" s="2">
+        <v>1800000</v>
+      </c>
+      <c r="F72" s="2">
+        <v>1800000</v>
+      </c>
+      <c r="G72" s="3">
+        <v>300000</v>
+      </c>
+      <c r="H72" s="4">
+        <v>1000000</v>
+      </c>
+      <c r="I72" s="2">
+        <v>600000</v>
+      </c>
+      <c r="J72" s="2"/>
+      <c r="K72" s="2">
+        <v>1900000</v>
+      </c>
+      <c r="L72" s="2">
+        <v>2600000</v>
+      </c>
+      <c r="M72" t="s">
+        <v>161</v>
+      </c>
+      <c r="N72" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>166</v>
+      </c>
+      <c r="B73" t="s">
+        <v>167</v>
+      </c>
+      <c r="C73" s="2">
+        <v>2200000</v>
+      </c>
+      <c r="D73" s="2">
+        <v>2200000</v>
+      </c>
+      <c r="E73" s="2">
+        <v>2600000</v>
+      </c>
+      <c r="F73" s="2">
+        <v>2600000</v>
+      </c>
+      <c r="G73" s="3">
+        <v>400000</v>
+      </c>
+      <c r="H73" s="4">
+        <v>1000000</v>
+      </c>
+      <c r="I73" s="2">
+        <v>800000</v>
+      </c>
+      <c r="J73" s="2"/>
+      <c r="K73" s="2">
+        <v>2600000</v>
+      </c>
+      <c r="L73" s="2">
+        <v>3200000</v>
+      </c>
+      <c r="M73" t="s">
+        <v>161</v>
+      </c>
+      <c r="N73" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>168</v>
+      </c>
+      <c r="B74" t="s">
+        <v>169</v>
+      </c>
+      <c r="C74" s="2">
+        <v>3500000</v>
+      </c>
+      <c r="D74" s="2">
+        <v>3500000</v>
+      </c>
+      <c r="E74" s="2">
+        <v>4000000</v>
+      </c>
+      <c r="F74" s="2">
+        <v>4000000</v>
+      </c>
+      <c r="G74" s="3">
+        <v>500000</v>
+      </c>
+      <c r="H74" s="4">
+        <v>1000000</v>
+      </c>
+      <c r="I74" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="J74" s="2"/>
+      <c r="K74" s="2">
+        <v>4000000</v>
+      </c>
+      <c r="L74" s="2">
+        <v>4500000</v>
+      </c>
+      <c r="M74" t="s">
+        <v>161</v>
+      </c>
+      <c r="N74" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>170</v>
+      </c>
+      <c r="B75" t="s">
+        <v>171</v>
+      </c>
+      <c r="C75" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="D75" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="E75" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="F75" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="G75" s="3">
+        <v>400000</v>
+      </c>
+      <c r="H75" s="4">
+        <v>1000000</v>
+      </c>
+      <c r="I75" s="2">
+        <v>800000</v>
+      </c>
+      <c r="J75" s="2"/>
+      <c r="K75" s="2">
+        <v>2400000</v>
+      </c>
+      <c r="L75" s="2">
+        <v>3000000</v>
+      </c>
+      <c r="M75" t="s">
+        <v>161</v>
+      </c>
+      <c r="N75" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>172</v>
+      </c>
+      <c r="B76" t="s">
+        <v>173</v>
+      </c>
+      <c r="C76" s="3">
+        <v>2200000</v>
+      </c>
+      <c r="D76" s="4">
+        <v>1800000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3000000</v>
+      </c>
+      <c r="F76" s="4">
+        <v>2200000</v>
+      </c>
+      <c r="G76" s="3">
+        <v>400000</v>
+      </c>
+      <c r="H76" s="4">
+        <v>500000</v>
+      </c>
+      <c r="I76" s="3">
+        <v>800000</v>
+      </c>
+      <c r="J76" s="4">
+        <v>1000000</v>
+      </c>
+      <c r="K76" s="2">
+        <v>2600000</v>
+      </c>
+      <c r="L76" s="2">
+        <v>2300000</v>
+      </c>
+      <c r="M76" t="s">
+        <v>174</v>
+      </c>
+      <c r="N76" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>175</v>
+      </c>
+      <c r="B77" t="s">
+        <v>176</v>
+      </c>
+      <c r="C77" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="D77" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="E77" s="3">
+        <v>2600000</v>
+      </c>
+      <c r="F77" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="G77" s="3">
+        <v>400000</v>
+      </c>
+      <c r="H77" s="4">
+        <v>500000</v>
+      </c>
+      <c r="I77" s="3">
+        <v>800000</v>
+      </c>
+      <c r="J77" s="4">
+        <v>1000000</v>
+      </c>
+      <c r="K77" s="2">
+        <v>2400000</v>
+      </c>
+      <c r="L77" s="2">
+        <v>2500000</v>
+      </c>
+      <c r="M77" t="s">
+        <v>174</v>
+      </c>
+      <c r="N77" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>177</v>
+      </c>
+      <c r="B78" t="s">
+        <v>178</v>
+      </c>
+      <c r="C78" s="3">
+        <v>1800000</v>
+      </c>
+      <c r="D78" s="4">
+        <v>1500000</v>
+      </c>
+      <c r="E78" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="F78" s="4">
+        <v>1800000</v>
+      </c>
+      <c r="G78" s="3">
+        <v>300000</v>
+      </c>
+      <c r="H78" s="4">
+        <v>500000</v>
+      </c>
+      <c r="I78" s="3">
+        <v>600000</v>
+      </c>
+      <c r="J78" s="4">
+        <v>1000000</v>
+      </c>
+      <c r="K78" s="2">
+        <v>2100000</v>
+      </c>
+      <c r="L78" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="M78" t="s">
+        <v>174</v>
+      </c>
+      <c r="N78" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>179</v>
+      </c>
+      <c r="B79" t="s">
+        <v>180</v>
+      </c>
+      <c r="C79" s="2">
+        <v>1600000</v>
+      </c>
+      <c r="D79" s="2">
+        <v>1600000</v>
+      </c>
+      <c r="E79" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="F79" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="G79" s="3">
+        <v>300000</v>
+      </c>
+      <c r="H79" s="4">
+        <v>500000</v>
+      </c>
+      <c r="I79" s="3">
+        <v>600000</v>
+      </c>
+      <c r="J79" s="4">
+        <v>1000000</v>
+      </c>
+      <c r="K79" s="2">
+        <v>1900000</v>
+      </c>
+      <c r="L79" s="2">
+        <v>2100000</v>
+      </c>
+      <c r="M79" t="s">
+        <v>174</v>
+      </c>
+      <c r="N79" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>181</v>
+      </c>
+      <c r="B80" t="s">
+        <v>182</v>
+      </c>
+      <c r="C80" s="3">
+        <v>900000</v>
+      </c>
+      <c r="D80" s="4">
+        <v>800000</v>
+      </c>
+      <c r="E80" s="3">
+        <v>1200000</v>
+      </c>
+      <c r="F80" s="4">
+        <v>800000</v>
+      </c>
+      <c r="G80" s="3">
+        <v>150000</v>
+      </c>
+      <c r="H80" s="4">
+        <v>500000</v>
+      </c>
+      <c r="I80" s="3">
+        <v>300000</v>
+      </c>
+      <c r="J80" s="4">
+        <v>1000000</v>
+      </c>
+      <c r="K80" s="2">
+        <v>1050000</v>
+      </c>
+      <c r="L80" s="2">
+        <v>1300000</v>
+      </c>
+      <c r="M80" t="s">
+        <v>174</v>
+      </c>
+      <c r="N80" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>183</v>
+      </c>
+      <c r="B81" t="s">
+        <v>184</v>
+      </c>
+      <c r="C81" s="3">
+        <v>2200000</v>
+      </c>
+      <c r="D81" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>3500000</v>
+      </c>
+      <c r="F81" s="4">
+        <v>2000000</v>
+      </c>
+      <c r="G81" s="3">
+        <v>400000</v>
+      </c>
+      <c r="H81" s="4">
+        <v>500000</v>
+      </c>
+      <c r="I81" s="3">
+        <v>800000</v>
+      </c>
+      <c r="J81" s="4">
+        <v>1000000</v>
+      </c>
+      <c r="K81" s="2">
+        <v>2600000</v>
+      </c>
+      <c r="L81" s="2">
+        <v>2500000</v>
+      </c>
+      <c r="M81" t="s">
+        <v>174</v>
+      </c>
+      <c r="N81" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>185</v>
+      </c>
+      <c r="B82" t="s">
+        <v>186</v>
+      </c>
+      <c r="C82" s="3">
+        <v>800000</v>
+      </c>
+      <c r="D82" s="4">
+        <v>700000</v>
+      </c>
+      <c r="E82" s="3">
+        <v>1200000</v>
+      </c>
+      <c r="F82" s="4">
+        <v>700000</v>
+      </c>
+      <c r="G82" s="3">
+        <v>150000</v>
+      </c>
+      <c r="H82" s="4">
+        <v>500000</v>
+      </c>
+      <c r="I82" s="3">
+        <v>300000</v>
+      </c>
+      <c r="J82" s="4">
+        <v>1000000</v>
+      </c>
+      <c r="K82" s="2">
+        <v>950000</v>
+      </c>
+      <c r="L82" s="2">
+        <v>1200000</v>
+      </c>
+      <c r="M82" t="s">
+        <v>174</v>
+      </c>
+      <c r="N82" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>187</v>
+      </c>
+      <c r="B83" t="s">
+        <v>188</v>
+      </c>
+      <c r="C83" s="3">
+        <v>900000</v>
+      </c>
+      <c r="D83" s="4">
+        <v>700000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1200000</v>
+      </c>
+      <c r="F83" s="4">
+        <v>700000</v>
+      </c>
+      <c r="G83" s="3">
+        <v>150000</v>
+      </c>
+      <c r="H83" s="4">
+        <v>500000</v>
+      </c>
+      <c r="I83" s="3">
+        <v>300000</v>
+      </c>
+      <c r="J83" s="4">
+        <v>1000000</v>
+      </c>
+      <c r="K83" s="2">
+        <v>1050000</v>
+      </c>
+      <c r="L83" s="2">
+        <v>1200000</v>
+      </c>
+      <c r="M83" t="s">
+        <v>174</v>
+      </c>
+      <c r="N83" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>189</v>
+      </c>
+      <c r="B84" t="s">
+        <v>190</v>
+      </c>
+      <c r="C84" s="3">
+        <v>1700000</v>
+      </c>
+      <c r="D84" s="4">
+        <v>1200000</v>
+      </c>
+      <c r="E84" s="3">
+        <v>2200000</v>
+      </c>
+      <c r="F84" s="4">
+        <v>1500000</v>
+      </c>
+      <c r="G84" s="3">
+        <v>300000</v>
+      </c>
+      <c r="H84" s="4">
+        <v>500000</v>
+      </c>
+      <c r="I84" s="3">
+        <v>600000</v>
+      </c>
+      <c r="J84" s="4">
+        <v>1000000</v>
+      </c>
+      <c r="K84" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="L84" s="2">
+        <v>1700000</v>
+      </c>
+      <c r="M84" t="s">
+        <v>174</v>
+      </c>
+      <c r="N84" t="s">
         <v>17</v>
       </c>
     </row>
